--- a/examples/Tesla DCF.xlsx
+++ b/examples/Tesla DCF.xlsx
@@ -84,7 +84,7 @@
     <t>Beta</t>
   </si>
   <si>
-    <t>Judgment: 5-year monthly regression against the S&amp;P 500 gives 1.77</t>
+    <t>Judgment: 5-year monthly regression against the MASI gives 1.77</t>
   </si>
   <si>
     <t>Equity risk premium</t>
